--- a/BAU_Lahan.xlsx
+++ b/BAU_Lahan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{2CD1BB71-2C25-4480-BEC2-AEB7909775E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BDAD650-965C-4500-802C-F875A12349F1}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{2CD1BB71-2C25-4480-BEC2-AEB7909775E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E960D0-561D-4006-945C-4B77ED499A6F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5B932833-3721-49C5-97AD-73DB152F560E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{5B932833-3721-49C5-97AD-73DB152F560E}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU_Lahan" sheetId="1" r:id="rId1"/>
@@ -920,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6FF615A-3B6D-467B-8F19-8F4D386BC3A9}">
-  <dimension ref="A1:AB28"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
@@ -928,7 +928,7 @@
     <col min="4" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1001,20 +1001,8 @@
       <c r="X1" s="4">
         <v>2045</v>
       </c>
-      <c r="Y1" s="4">
-        <v>2046</v>
-      </c>
-      <c r="Z1" s="4">
-        <v>2047</v>
-      </c>
-      <c r="AA1" s="4">
-        <v>2048</v>
-      </c>
-      <c r="AB1" s="4">
-        <v>2049</v>
-      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1022,85 +1010,73 @@
         <v>2</v>
       </c>
       <c r="C2" s="8">
-        <v>1463618</v>
+        <v>1464013</v>
       </c>
       <c r="D2" s="9">
-        <v>1456688.4943748692</v>
+        <v>1452493.5410596021</v>
       </c>
       <c r="E2" s="9">
-        <v>1449791.7965234939</v>
+        <v>1441064.7219798334</v>
       </c>
       <c r="F2" s="9">
-        <v>1442927.7511173305</v>
+        <v>1429725.8295688352</v>
       </c>
       <c r="G2" s="9">
-        <v>1436096.2035632385</v>
+        <v>1418476.1562464368</v>
       </c>
       <c r="H2" s="9">
-        <v>1429296.9999999998</v>
+        <v>1407315.0000000002</v>
       </c>
       <c r="I2" s="5">
-        <v>1422564.0649465448</v>
+        <v>1396326.3301057024</v>
       </c>
       <c r="J2" s="5">
-        <v>1415862.8464743418</v>
+        <v>1385423.4625129832</v>
       </c>
       <c r="K2" s="5">
-        <v>1409193.1951772971</v>
+        <v>1374605.7272558659</v>
       </c>
       <c r="L2" s="5">
-        <v>1402554.9623531187</v>
+        <v>1363872.4595996372</v>
       </c>
       <c r="M2" s="5">
-        <v>1395948.0000000005</v>
+        <v>1353222.9999999995</v>
       </c>
       <c r="N2" s="6">
-        <v>1389405.9689755284</v>
+        <v>1343687.3555781324</v>
       </c>
       <c r="O2" s="6">
-        <v>1382894.5968079232</v>
+        <v>1334218.9051919414</v>
       </c>
       <c r="P2" s="6">
-        <v>1376413.739816193</v>
+        <v>1324817.1753507815</v>
       </c>
       <c r="Q2" s="6">
-        <v>1369963.2549926993</v>
+        <v>1315481.695900515</v>
       </c>
       <c r="R2" s="6">
-        <v>1363543</v>
+        <v>1306211.9999999998</v>
       </c>
       <c r="S2" s="7">
-        <v>1357187.6317295134</v>
+        <v>1300409.6093175323</v>
       </c>
       <c r="T2" s="7">
-        <v>1350861.8853380973</v>
+        <v>1294632.9937294843</v>
       </c>
       <c r="U2" s="7">
-        <v>1344565.6227604686</v>
+        <v>1288882.0387389995</v>
       </c>
       <c r="V2" s="7">
-        <v>1338298.7065748558</v>
+        <v>1283156.630357834</v>
       </c>
       <c r="W2" s="7">
-        <v>1332060.9999999998</v>
+        <v>1277456.6551040967</v>
       </c>
       <c r="X2" s="10">
-        <v>1325949.5789792424</v>
-      </c>
-      <c r="Y2" s="10">
-        <v>1319866.1968147333</v>
-      </c>
-      <c r="Z2" s="10">
-        <v>1313810.7248657756</v>
-      </c>
-      <c r="AA2" s="10">
-        <v>1307783.0350818683</v>
-      </c>
-      <c r="AB2" s="10">
-        <v>1301782.9999999995</v>
+        <v>1271782.0000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1108,85 +1084,73 @@
         <v>3</v>
       </c>
       <c r="C3" s="8">
-        <v>336061</v>
+        <v>346362</v>
       </c>
       <c r="D3" s="9">
-        <v>335973.75471200503</v>
+        <v>341672.73503375478</v>
       </c>
       <c r="E3" s="9">
-        <v>335886.53207388695</v>
+        <v>337046.95626381185</v>
       </c>
       <c r="F3" s="9">
-        <v>335799.33207976562</v>
+        <v>332483.80417441553</v>
       </c>
       <c r="G3" s="9">
-        <v>335712.15472376236</v>
+        <v>327982.43088647106</v>
       </c>
       <c r="H3" s="9">
-        <v>335625.00000000006</v>
+        <v>323542.00000000006</v>
       </c>
       <c r="I3" s="5">
-        <v>335813.78749632987</v>
+        <v>322862.95564283582</v>
       </c>
       <c r="J3" s="5">
-        <v>336002.68118474545</v>
+        <v>322185.3364522311</v>
       </c>
       <c r="K3" s="5">
-        <v>336191.68112497928</v>
+        <v>321509.13943707099</v>
       </c>
       <c r="L3" s="5">
-        <v>336380.78737679753</v>
+        <v>320834.3616125182</v>
       </c>
       <c r="M3" s="5">
-        <v>336570</v>
+        <v>320161</v>
       </c>
       <c r="N3" s="6">
-        <v>337922.48646037217</v>
+        <v>321009.88651153113</v>
       </c>
       <c r="O3" s="6">
-        <v>339280.40780687646</v>
+        <v>321861.02379161143</v>
       </c>
       <c r="P3" s="6">
-        <v>340643.7858792785</v>
+        <v>322714.41780801036</v>
       </c>
       <c r="Q3" s="6">
-        <v>342012.64260510565</v>
+        <v>323570.0745443207</v>
       </c>
       <c r="R3" s="6">
-        <v>343386.99999999977</v>
+        <v>324428.00000000017</v>
       </c>
       <c r="S3" s="7">
-        <v>345094.92565143661</v>
+        <v>323508.50954178668</v>
       </c>
       <c r="T3" s="7">
-        <v>346811.34612076334</v>
+        <v>322591.62509385223</v>
       </c>
       <c r="U3" s="7">
-        <v>348536.30365919345</v>
+        <v>321677.33927026944</v>
       </c>
       <c r="V3" s="7">
-        <v>350269.84072808782</v>
+        <v>320765.64470604423</v>
       </c>
       <c r="W3" s="7">
-        <v>352012</v>
+        <v>319856.5340570563</v>
       </c>
       <c r="X3" s="10">
-        <v>353843.24748093419</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>355684.02153294103</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>357534.37171543692</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>359394.34784565773</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>361264.00000000006</v>
+        <v>318950.00000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1197,82 +1161,70 @@
         <v>691</v>
       </c>
       <c r="D4" s="9">
-        <v>681.54475641740169</v>
+        <v>688.17702842789072</v>
       </c>
       <c r="E4" s="9">
-        <v>672.21889290890795</v>
+        <v>685.36558966113159</v>
       </c>
       <c r="F4" s="9">
-        <v>663.02063911255732</v>
+        <v>682.56563658426433</v>
       </c>
       <c r="G4" s="9">
-        <v>653.9482488909955</v>
+        <v>679.77712227431346</v>
       </c>
       <c r="H4" s="9">
-        <v>644.99999999999989</v>
+        <v>677</v>
       </c>
       <c r="I4" s="5">
-        <v>638.26062938752273</v>
+        <v>681.5387336092906</v>
       </c>
       <c r="J4" s="5">
-        <v>631.59167600954515</v>
+        <v>686.10789573080581</v>
       </c>
       <c r="K4" s="5">
-        <v>624.99240410197308</v>
+        <v>690.70769036293734</v>
       </c>
       <c r="L4" s="5">
-        <v>618.46208558844387</v>
+        <v>695.33832287171981</v>
       </c>
       <c r="M4" s="5">
-        <v>612.00000000000023</v>
+        <v>699.99999999999989</v>
       </c>
       <c r="N4" s="6">
-        <v>610.18931736648938</v>
+        <v>705.12442104998274</v>
       </c>
       <c r="O4" s="6">
-        <v>608.38399187611481</v>
+        <v>710.28635594439049</v>
       </c>
       <c r="P4" s="6">
-        <v>606.58400767906255</v>
+        <v>715.48607930712899</v>
       </c>
       <c r="Q4" s="6">
-        <v>604.78934897241254</v>
+        <v>720.72386777251631</v>
       </c>
       <c r="R4" s="6">
-        <v>602.99999999999989</v>
+        <v>725.99999999999989</v>
       </c>
       <c r="S4" s="7">
-        <v>601.59345352018659</v>
+        <v>730.59339491450976</v>
       </c>
       <c r="T4" s="7">
-        <v>600.19018792428676</v>
+        <v>735.21585219381382</v>
       </c>
       <c r="U4" s="7">
-        <v>598.79019555937225</v>
+        <v>739.86755571521053</v>
       </c>
       <c r="V4" s="7">
-        <v>597.39346879036589</v>
+        <v>744.54869051938817</v>
       </c>
       <c r="W4" s="7">
-        <v>596</v>
+        <v>749.25944281778573</v>
       </c>
       <c r="X4" s="10">
-        <v>594.5933760850354</v>
-      </c>
-      <c r="Y4" s="10">
-        <v>593.19007195335621</v>
-      </c>
-      <c r="Z4" s="10">
-        <v>591.79007976991795</v>
-      </c>
-      <c r="AA4" s="10">
-        <v>590.39339171816766</v>
-      </c>
-      <c r="AB4" s="10">
-        <v>589.00000000000011</v>
+        <v>754.00000000000011</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1280,85 +1232,73 @@
         <v>5</v>
       </c>
       <c r="C5" s="8">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="D5" s="9">
-        <v>1634.7874231647386</v>
+        <v>1653.4394922616245</v>
       </c>
       <c r="E5" s="9">
-        <v>1631.5811470925557</v>
+        <v>1664.9586812243474</v>
       </c>
       <c r="F5" s="9">
-        <v>1628.38115942589</v>
+        <v>1676.5581221194695</v>
       </c>
       <c r="G5" s="9">
-        <v>1625.1874478314164</v>
+        <v>1688.2383740464788</v>
       </c>
       <c r="H5" s="9">
-        <v>1621.9999999999995</v>
+        <v>1700.0000000000002</v>
       </c>
       <c r="I5" s="5">
-        <v>1621.1992096811136</v>
+        <v>1714.7420916562571</v>
       </c>
       <c r="J5" s="5">
-        <v>1620.3988147168111</v>
+        <v>1729.6120240574562</v>
       </c>
       <c r="K5" s="5">
-        <v>1619.5988149119034</v>
+        <v>1744.61090581535</v>
       </c>
       <c r="L5" s="5">
-        <v>1618.7992100712986</v>
+        <v>1759.7398551553708</v>
       </c>
       <c r="M5" s="5">
-        <v>1618.0000000000002</v>
+        <v>1774.9999999999998</v>
       </c>
       <c r="N5" s="6">
-        <v>1617.7999505378991</v>
+        <v>1790.33280616499</v>
       </c>
       <c r="O5" s="6">
-        <v>1617.5999258099066</v>
+        <v>1805.7980601862578</v>
       </c>
       <c r="P5" s="6">
-        <v>1617.3999258129643</v>
+        <v>1821.3969061749624</v>
       </c>
       <c r="Q5" s="6">
-        <v>1617.1999505440144</v>
+        <v>1837.1304981253247</v>
       </c>
       <c r="R5" s="6">
-        <v>1616.9999999999998</v>
+        <v>1852.9999999999991</v>
       </c>
       <c r="S5" s="7">
-        <v>1616.7999505072989</v>
+        <v>1868.0254282441838</v>
       </c>
       <c r="T5" s="7">
-        <v>1616.5999257640101</v>
+        <v>1883.1726932363013</v>
       </c>
       <c r="U5" s="7">
-        <v>1616.3999257670716</v>
+        <v>1898.4427829144599</v>
       </c>
       <c r="V5" s="7">
-        <v>1616.199950513422</v>
+        <v>1913.8366932276654</v>
       </c>
       <c r="W5" s="7">
-        <v>1615.9999999999998</v>
+        <v>1929.3554282007783</v>
       </c>
       <c r="X5" s="10">
-        <v>1615.7999504766608</v>
-      </c>
-      <c r="Y5" s="10">
-        <v>1615.599925718057</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>1615.3999257211224</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>1615.1999504827918</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>1615.0000000000002</v>
+        <v>1944.9999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1366,85 +1306,73 @@
         <v>6</v>
       </c>
       <c r="C6" s="8">
-        <v>3747</v>
+        <v>3755</v>
       </c>
       <c r="D6" s="9">
-        <v>3745.5989526555459</v>
+        <v>3734.9878250645406</v>
       </c>
       <c r="E6" s="9">
-        <v>3744.1984291791628</v>
+        <v>3715.0823044954323</v>
       </c>
       <c r="F6" s="9">
-        <v>3742.7984293749701</v>
+        <v>3695.2828698810004</v>
       </c>
       <c r="G6" s="9">
-        <v>3741.3989530471604</v>
+        <v>3675.5889558389058</v>
       </c>
       <c r="H6" s="9">
-        <v>3740</v>
+        <v>3656.0000000000005</v>
       </c>
       <c r="I6" s="5">
-        <v>3738.5989506930709</v>
+        <v>3642.2976743081667</v>
       </c>
       <c r="J6" s="5">
-        <v>3737.1984262361848</v>
+        <v>3628.6467035751316</v>
       </c>
       <c r="K6" s="5">
-        <v>3735.7984264327265</v>
+        <v>3615.0468953275977</v>
       </c>
       <c r="L6" s="5">
-        <v>3734.3989510861543</v>
+        <v>3601.4980578136401</v>
       </c>
       <c r="M6" s="5">
-        <v>3733.0000000000005</v>
+        <v>3588.0000000000005</v>
       </c>
       <c r="N6" s="6">
-        <v>3731.5989487232273</v>
+        <v>3579.9640850262217</v>
       </c>
       <c r="O6" s="6">
-        <v>3730.1984232821578</v>
+        <v>3571.9461678031307</v>
       </c>
       <c r="P6" s="6">
-        <v>3728.7984234794376</v>
+        <v>3563.94620802181</v>
       </c>
       <c r="Q6" s="6">
-        <v>3727.3989491177867</v>
+        <v>3555.9641654636207</v>
       </c>
       <c r="R6" s="6">
-        <v>3725.9999999999991</v>
+        <v>3548.0000000000009</v>
       </c>
       <c r="S6" s="7">
-        <v>3724.5989467459744</v>
+        <v>3540.6284839208938</v>
       </c>
       <c r="T6" s="7">
-        <v>3723.1984203170214</v>
+        <v>3533.2722833010052</v>
       </c>
       <c r="U6" s="7">
-        <v>3721.7984205150437</v>
+        <v>3525.9313663201106</v>
       </c>
       <c r="V6" s="7">
-        <v>3720.3989471420191</v>
+        <v>3518.6057012240976</v>
       </c>
       <c r="W6" s="7">
-        <v>3718.9999999999991</v>
+        <v>3511.2952563248282</v>
       </c>
       <c r="X6" s="10">
-        <v>3717.5989447612687</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>3716.1984173407104</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>3714.7984175394799</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>3713.3989451588077</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>3711.9999999999986</v>
+        <v>3504.0000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1452,85 +1380,73 @@
         <v>7</v>
       </c>
       <c r="C7" s="8">
-        <v>2213</v>
+        <v>2489</v>
       </c>
       <c r="D7" s="9">
-        <v>2210.9963751654504</v>
+        <v>2504.6031425889914</v>
       </c>
       <c r="E7" s="9">
-        <v>2208.9945643898604</v>
+        <v>2520.3040987812983</v>
       </c>
       <c r="F7" s="9">
-        <v>2206.9945660308017</v>
+        <v>2536.1034817547429</v>
       </c>
       <c r="G7" s="9">
-        <v>2204.9963784473334</v>
+        <v>2552.0019085310614</v>
       </c>
       <c r="H7" s="9">
-        <v>2203</v>
+        <v>2568</v>
       </c>
       <c r="I7" s="5">
-        <v>2201.5982172083031</v>
+        <v>2579.4966005713432</v>
       </c>
       <c r="J7" s="5">
-        <v>2200.1973263798359</v>
+        <v>2591.0446699217741</v>
       </c>
       <c r="K7" s="5">
-        <v>2198.7973269470367</v>
+        <v>2602.6444384702936</v>
       </c>
       <c r="L7" s="5">
-        <v>2197.3982183427047</v>
+        <v>2614.2961376674589</v>
       </c>
       <c r="M7" s="5">
-        <v>2196</v>
+        <v>2626.0000000000009</v>
       </c>
       <c r="N7" s="6">
-        <v>2195.7999635601709</v>
+        <v>2631.9727683219821</v>
       </c>
       <c r="O7" s="6">
-        <v>2195.5999453419163</v>
+        <v>2637.9591215493065</v>
       </c>
       <c r="P7" s="6">
-        <v>2195.3999453435758</v>
+        <v>2643.9590905804848</v>
       </c>
       <c r="Q7" s="6">
-        <v>2195.1999635634902</v>
+        <v>2649.9727063843065</v>
       </c>
       <c r="R7" s="6">
-        <v>2195</v>
+        <v>2655.9999999999995</v>
       </c>
       <c r="S7" s="7">
-        <v>2194.7999635435649</v>
+        <v>2661.4717410410526</v>
       </c>
       <c r="T7" s="7">
-        <v>2194.5999453170089</v>
+        <v>2666.9547546536492</v>
       </c>
       <c r="U7" s="7">
-        <v>2194.3999453186702</v>
+        <v>2672.4490640609042</v>
       </c>
       <c r="V7" s="7">
-        <v>2194.1999635468878</v>
+        <v>2677.954692533775</v>
       </c>
       <c r="W7" s="7">
-        <v>2194.0000000000005</v>
+        <v>2683.4716633911607</v>
       </c>
       <c r="X7" s="10">
-        <v>2193.7999635269443</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>2193.5999452920792</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>2193.3999452937419</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>2193.1999635302695</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>2193</v>
+        <v>2689.0000000000009</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:24">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1538,85 +1454,73 @@
         <v>8</v>
       </c>
       <c r="C8" s="8">
-        <v>72512</v>
+        <v>61261</v>
       </c>
       <c r="D8" s="9">
-        <v>74722.638388411651</v>
+        <v>63997.21195442466</v>
       </c>
       <c r="E8" s="9">
-        <v>77000.671443696643</v>
+        <v>66855.636341874182</v>
       </c>
       <c r="F8" s="9">
-        <v>79348.153794575235</v>
+        <v>69841.731759502101</v>
       </c>
       <c r="G8" s="9">
-        <v>81767.202708243043</v>
+        <v>72961.200611758351</v>
       </c>
       <c r="H8" s="9">
-        <v>84259.999999999985</v>
+        <v>76219.999999999956</v>
       </c>
       <c r="I8" s="5">
-        <v>86038.150345116257</v>
+        <v>77637.487421032856</v>
       </c>
       <c r="J8" s="5">
-        <v>87853.825241025741</v>
+        <v>79081.336303477234</v>
       </c>
       <c r="K8" s="5">
-        <v>89707.81657347428</v>
+        <v>80552.036899759682</v>
       </c>
       <c r="L8" s="5">
-        <v>91600.932939481281</v>
+        <v>82050.088579685995</v>
       </c>
       <c r="M8" s="5">
-        <v>93534.000000000044</v>
+        <v>83576.000000000044</v>
       </c>
       <c r="N8" s="6">
-        <v>94859.874005579317</v>
+        <v>84504.345871125624</v>
       </c>
       <c r="O8" s="6">
-        <v>96204.542694147385</v>
+        <v>85443.003626720907</v>
       </c>
       <c r="P8" s="6">
-        <v>97568.272486274465</v>
+        <v>86392.087809182834</v>
       </c>
       <c r="Q8" s="6">
-        <v>98951.333579126585</v>
+        <v>87351.714233222956</v>
       </c>
       <c r="R8" s="6">
-        <v>100353.99999999997</v>
+        <v>88322</v>
       </c>
       <c r="S8" s="7">
-        <v>101520.75254727996</v>
+        <v>89201.004074191616</v>
       </c>
       <c r="T8" s="7">
-        <v>102701.07018919077</v>
+        <v>90088.756231108317</v>
       </c>
       <c r="U8" s="7">
-        <v>103895.11063851631</v>
+        <v>90985.343534</v>
       </c>
       <c r="V8" s="7">
-        <v>105103.03344166737</v>
+        <v>91890.853912593215</v>
       </c>
       <c r="W8" s="7">
-        <v>106325.00000000003</v>
+        <v>92805.376171714568</v>
       </c>
       <c r="X8" s="10">
-        <v>107295.51999097374</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>108274.89875507588</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>109263.21715397036</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>110260.55678741526</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>111267.00000000006</v>
+        <v>93728.999999999956</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1624,85 +1528,73 @@
         <v>9</v>
       </c>
       <c r="C9" s="8">
-        <v>2803</v>
+        <v>2730</v>
       </c>
       <c r="D9" s="9">
-        <v>2840.5787904899476</v>
+        <v>2890.5680445147304</v>
       </c>
       <c r="E9" s="9">
-        <v>2878.6613860083244</v>
+        <v>3060.5800805749864</v>
       </c>
       <c r="F9" s="9">
-        <v>2917.2545408839251</v>
+        <v>3240.5915672484889</v>
       </c>
       <c r="G9" s="9">
-        <v>2956.3650999983474</v>
+        <v>3431.1906335576523</v>
       </c>
       <c r="H9" s="9">
-        <v>2995.9999999999995</v>
+        <v>3633.0000000000009</v>
       </c>
       <c r="I9" s="5">
-        <v>3047.405440560457</v>
+        <v>3813.8712547567698</v>
       </c>
       <c r="J9" s="5">
-        <v>3099.6928969150445</v>
+        <v>4003.7473019157655</v>
       </c>
       <c r="K9" s="5">
-        <v>3152.8775027121196</v>
+        <v>4203.0764508908651</v>
       </c>
       <c r="L9" s="5">
-        <v>3206.9746512635447</v>
+        <v>4412.3293304700728</v>
       </c>
       <c r="M9" s="5">
-        <v>3262</v>
+        <v>4631.9999999999982</v>
       </c>
       <c r="N9" s="6">
-        <v>3315.2339205067856</v>
+        <v>4833.9970194894522</v>
       </c>
       <c r="O9" s="6">
-        <v>3369.336587271242</v>
+        <v>5044.8029327359473</v>
       </c>
       <c r="P9" s="6">
-        <v>3424.3221777210892</v>
+        <v>5264.8018870373962</v>
       </c>
       <c r="Q9" s="6">
-        <v>3480.2051006513243</v>
+        <v>5494.3947819821287</v>
       </c>
       <c r="R9" s="6">
-        <v>3537.0000000000005</v>
+        <v>5734.0000000000018</v>
       </c>
       <c r="S9" s="7">
-        <v>3584.8857236986992</v>
+        <v>5935.8751812156715</v>
       </c>
       <c r="T9" s="7">
-        <v>3633.4197489337703</v>
+        <v>6144.8577200858354</v>
       </c>
       <c r="U9" s="7">
-        <v>3682.6108527445813</v>
+        <v>6361.1978431738798</v>
       </c>
       <c r="V9" s="7">
-        <v>3732.46793099857</v>
+        <v>6585.1545866931447</v>
       </c>
       <c r="W9" s="7">
-        <v>3782.9999999999986</v>
+        <v>6816.9961066655706</v>
       </c>
       <c r="X9" s="10">
-        <v>3828.1112165180866</v>
-      </c>
-      <c r="Y9" s="10">
-        <v>3873.7603716710523</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>3919.9538802266015</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>3966.6982334467502</v>
-      </c>
-      <c r="AB9" s="10">
-        <v>4013.9999999999973</v>
+        <v>7057.0000000000036</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1710,85 +1602,73 @@
         <v>10</v>
       </c>
       <c r="C10" s="8">
-        <v>38091</v>
+        <v>38119</v>
       </c>
       <c r="D10" s="9">
-        <v>38736.732326041907</v>
+        <v>40511.912143259498</v>
       </c>
       <c r="E10" s="9">
-        <v>39393.411338621198</v>
+        <v>43055.038838982568</v>
       </c>
       <c r="F10" s="9">
-        <v>40061.222609903481</v>
+        <v>45757.809773852598</v>
       </c>
       <c r="G10" s="9">
-        <v>40740.354857940438</v>
+        <v>48630.246581135318</v>
       </c>
       <c r="H10" s="9">
-        <v>41430.999999999993</v>
+        <v>51682.999999999993</v>
       </c>
       <c r="I10" s="5">
-        <v>41906.747889081758</v>
+        <v>53598.632310291723</v>
       </c>
       <c r="J10" s="5">
-        <v>42387.958741982053</v>
+        <v>55585.267603154767</v>
       </c>
       <c r="K10" s="5">
-        <v>42874.695289349547</v>
+        <v>57645.537606769394</v>
       </c>
       <c r="L10" s="5">
-        <v>43367.020982162459</v>
+        <v>59782.171594418411</v>
       </c>
       <c r="M10" s="5">
-        <v>43865.000000000022</v>
+        <v>61997.999999999971</v>
       </c>
       <c r="N10" s="6">
-        <v>44009.840323511926</v>
+        <v>63251.84823121137</v>
       </c>
       <c r="O10" s="6">
-        <v>44155.158903476949</v>
+        <v>64531.054302787139</v>
       </c>
       <c r="P10" s="6">
-        <v>44300.95731907709</v>
+        <v>65836.131051968638</v>
       </c>
       <c r="Q10" s="6">
-        <v>44447.23715470876</v>
+        <v>67167.601687623188</v>
       </c>
       <c r="R10" s="6">
-        <v>44593.999999999985</v>
+        <v>68525.999999999985</v>
       </c>
       <c r="S10" s="7">
-        <v>44704.451505200472</v>
+        <v>68729.976062686954</v>
       </c>
       <c r="T10" s="7">
-        <v>44815.176579378858</v>
+        <v>68934.559285198629</v>
       </c>
       <c r="U10" s="7">
-        <v>44926.175900117465</v>
+        <v>69139.751474820892</v>
       </c>
       <c r="V10" s="7">
-        <v>45037.450146676849</v>
+        <v>69345.554444219189</v>
       </c>
       <c r="W10" s="7">
-        <v>45148.999999999985</v>
+        <v>69551.970011454629</v>
       </c>
       <c r="X10" s="10">
-        <v>45295.644297309707</v>
-      </c>
-      <c r="Y10" s="10">
-        <v>45442.764896418659</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>45590.363344358731</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>45738.441193186576</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>45886.999999999949</v>
+        <v>69758.999999999956</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:24">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1799,82 +1679,70 @@
         <v>14970</v>
       </c>
       <c r="D11" s="9">
-        <v>15039.55072416403</v>
+        <v>15974.146167063105</v>
       </c>
       <c r="E11" s="9">
-        <v>15109.424581476473</v>
+        <v>17045.647679806072</v>
       </c>
       <c r="F11" s="9">
-        <v>15179.623073216186</v>
+        <v>18189.022548395609</v>
       </c>
       <c r="G11" s="9">
-        <v>15250.147707636976</v>
+        <v>19409.091838615772</v>
       </c>
       <c r="H11" s="9">
-        <v>15321.000000000007</v>
+        <v>20710.999999999996</v>
       </c>
       <c r="I11" s="5">
-        <v>15466.991114589293</v>
+        <v>21625.074791889103</v>
       </c>
       <c r="J11" s="5">
-        <v>15614.373352834942</v>
+        <v>22579.492045521583</v>
       </c>
       <c r="K11" s="5">
-        <v>15763.15997050962</v>
+        <v>23576.032265330949</v>
       </c>
       <c r="L11" s="5">
-        <v>15913.364349697926</v>
+        <v>24616.554537867432</v>
       </c>
       <c r="M11" s="5">
-        <v>16064.999999999991</v>
+        <v>25703.000000000015</v>
       </c>
       <c r="N11" s="6">
-        <v>16254.47741861885</v>
+        <v>26477.497087066786</v>
       </c>
       <c r="O11" s="6">
-        <v>16446.189614216626</v>
+        <v>27275.331750987436</v>
       </c>
       <c r="P11" s="6">
-        <v>16640.162944700154</v>
+        <v>28097.207212603589</v>
       </c>
       <c r="Q11" s="6">
-        <v>16836.424078852586</v>
+        <v>28943.847882598271</v>
       </c>
       <c r="R11" s="6">
-        <v>17035</v>
+        <v>29815.999999999993</v>
       </c>
       <c r="S11" s="7">
-        <v>17194.581967672533</v>
+        <v>30371.324776616653</v>
       </c>
       <c r="T11" s="7">
-        <v>17355.658881303752</v>
+        <v>30936.992510287382</v>
       </c>
       <c r="U11" s="7">
-        <v>17518.244745379579</v>
+        <v>31513.195839203614</v>
       </c>
       <c r="V11" s="7">
-        <v>17682.353695578389</v>
+        <v>32100.130989454574</v>
       </c>
       <c r="W11" s="7">
-        <v>17847.999999999996</v>
+        <v>32697.997841852084</v>
       </c>
       <c r="X11" s="10">
-        <v>17925.13047126984</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>18002.594263337436</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>18080.392816654949</v>
-      </c>
-      <c r="AA11" s="10">
-        <v>18158.527577899484</v>
-      </c>
-      <c r="AB11" s="10">
-        <v>18236.999999999989</v>
+        <v>33307</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:24">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1882,85 +1750,73 @@
         <v>12</v>
       </c>
       <c r="C12" s="8">
-        <v>12144</v>
+        <v>10981</v>
       </c>
       <c r="D12" s="9">
-        <v>12370.585401101505</v>
+        <v>11463.158097246234</v>
       </c>
       <c r="E12" s="9">
-        <v>12601.398482044277</v>
+        <v>11966.486983194784</v>
       </c>
       <c r="F12" s="9">
-        <v>12836.518123801021</v>
+        <v>12491.916233221105</v>
       </c>
       <c r="G12" s="9">
-        <v>13076.024679122842</v>
+        <v>13040.41623886442</v>
       </c>
       <c r="H12" s="9">
-        <v>13320.000000000002</v>
+        <v>13612.999999999996</v>
       </c>
       <c r="I12" s="5">
-        <v>13558.131880202225</v>
+        <v>14187.262320065363</v>
       </c>
       <c r="J12" s="5">
-        <v>13800.521027098794</v>
+        <v>14785.749808150036</v>
       </c>
       <c r="K12" s="5">
-        <v>14047.243551119318</v>
+        <v>15409.484399256644</v>
       </c>
       <c r="L12" s="5">
-        <v>14298.376923378075</v>
+        <v>16059.531138559381</v>
       </c>
       <c r="M12" s="5">
-        <v>14554.000000000007</v>
+        <v>16736.999999999996</v>
       </c>
       <c r="N12" s="6">
-        <v>14787.205749424253</v>
+        <v>17305.802436652713</v>
       </c>
       <c r="O12" s="6">
-        <v>15024.148266854863</v>
+        <v>17893.935470900102</v>
       </c>
       <c r="P12" s="6">
-        <v>15264.887428324766</v>
+        <v>18502.05604789445</v>
       </c>
       <c r="Q12" s="6">
-        <v>15509.484069289403</v>
+        <v>19130.843438892087</v>
       </c>
       <c r="R12" s="6">
-        <v>15758.000000000007</v>
+        <v>19781.000000000015</v>
       </c>
       <c r="S12" s="7">
-        <v>15923.295651312845</v>
+        <v>20363.698182724802</v>
       </c>
       <c r="T12" s="7">
-        <v>16090.325193496545</v>
+        <v>20963.561178762924</v>
       </c>
       <c r="U12" s="7">
-        <v>16259.106814431592</v>
+        <v>21581.094620060398</v>
       </c>
       <c r="V12" s="7">
-        <v>16429.658892782689</v>
+        <v>22216.81903320034</v>
       </c>
       <c r="W12" s="7">
-        <v>16602</v>
+        <v>22871.270278161242</v>
       </c>
       <c r="X12" s="10">
-        <v>16743.178417351042</v>
-      </c>
-      <c r="Y12" s="10">
-        <v>16885.557373524261</v>
-      </c>
-      <c r="Z12" s="10">
-        <v>17029.147077540911</v>
-      </c>
-      <c r="AA12" s="10">
-        <v>17173.957825236692</v>
-      </c>
-      <c r="AB12" s="10">
-        <v>17320.000000000004</v>
+        <v>23544.999999999993</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:24">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1971,82 +1827,70 @@
         <v>74927</v>
       </c>
       <c r="D13" s="9">
-        <v>75375.986712968661</v>
+        <v>75532.726839300201</v>
       </c>
       <c r="E13" s="9">
-        <v>75827.663898909974</v>
+        <v>76143.350511569137</v>
       </c>
       <c r="F13" s="9">
-        <v>76282.047680004427</v>
+        <v>76758.910603913682</v>
       </c>
       <c r="G13" s="9">
-        <v>76739.154275041772</v>
+        <v>77379.447023471846</v>
       </c>
       <c r="H13" s="9">
-        <v>77199</v>
+        <v>78005</v>
       </c>
       <c r="I13" s="5">
-        <v>77346.237293055601</v>
+        <v>78340.108362774423</v>
       </c>
       <c r="J13" s="5">
-        <v>77493.755403485338</v>
+        <v>78676.656346275748</v>
       </c>
       <c r="K13" s="5">
-        <v>77641.554866876337</v>
+        <v>79014.65013509398</v>
       </c>
       <c r="L13" s="5">
-        <v>77789.636219837208</v>
+        <v>79354.09594038807</v>
       </c>
       <c r="M13" s="5">
-        <v>77938.000000000015</v>
+        <v>79695</v>
       </c>
       <c r="N13" s="6">
-        <v>78099.330710799783</v>
+        <v>79972.855751094874</v>
       </c>
       <c r="O13" s="6">
-        <v>78260.995374206075</v>
+        <v>80251.680243245224</v>
       </c>
       <c r="P13" s="6">
-        <v>78422.994681496726</v>
+        <v>80531.476853956221</v>
       </c>
       <c r="Q13" s="6">
-        <v>78585.329325380488</v>
+        <v>80812.248972508649</v>
       </c>
       <c r="R13" s="6">
-        <v>78748.000000000029</v>
+        <v>81093.999999999985</v>
       </c>
       <c r="S13" s="7">
-        <v>79034.507608877539</v>
+        <v>81436.855626348799</v>
       </c>
       <c r="T13" s="7">
-        <v>79322.057613878729</v>
+        <v>81781.160804828702</v>
       </c>
       <c r="U13" s="7">
-        <v>79610.653807536975</v>
+        <v>82126.921663970832</v>
       </c>
       <c r="V13" s="7">
-        <v>79900.299996183996</v>
+        <v>82474.144358217018</v>
       </c>
       <c r="W13" s="7">
-        <v>80191.000000000029</v>
+        <v>82822.835068029308</v>
       </c>
       <c r="X13" s="10">
-        <v>80431.552472615367</v>
-      </c>
-      <c r="Y13" s="10">
-        <v>80672.826541071656</v>
-      </c>
-      <c r="Z13" s="10">
-        <v>80914.824369971699</v>
-      </c>
-      <c r="AA13" s="10">
-        <v>81157.548130411553</v>
-      </c>
-      <c r="AB13" s="10">
-        <v>81401.000000000015</v>
+        <v>83173.000000000015</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2054,85 +1898,73 @@
         <v>14</v>
       </c>
       <c r="C14" s="8">
-        <v>84707</v>
+        <v>81450</v>
       </c>
       <c r="D14" s="9">
-        <v>86118.002996107418</v>
+        <v>81506.72094519643</v>
       </c>
       <c r="E14" s="9">
-        <v>87552.509710384824</v>
+        <v>81563.481390277739</v>
       </c>
       <c r="F14" s="9">
-        <v>89010.911654947573</v>
+        <v>81620.281362751251</v>
       </c>
       <c r="G14" s="9">
-        <v>90493.606863506298</v>
+        <v>81677.120890143444</v>
       </c>
       <c r="H14" s="9">
-        <v>92001.000000000029</v>
+        <v>81733.999999999942</v>
       </c>
       <c r="I14" s="5">
-        <v>93432.739050265751</v>
+        <v>81240.066097615942</v>
       </c>
       <c r="J14" s="5">
-        <v>94886.759126912264</v>
+        <v>80749.117130508806</v>
       </c>
       <c r="K14" s="5">
-        <v>96363.40697199179</v>
+        <v>80261.135060154484</v>
       </c>
       <c r="L14" s="5">
-        <v>97863.03472362984</v>
+        <v>79776.101957039049</v>
       </c>
       <c r="M14" s="5">
-        <v>99386.000000000044</v>
+        <v>79294</v>
       </c>
       <c r="N14" s="6">
-        <v>99976.34501248227</v>
+        <v>78467.551145971389</v>
       </c>
       <c r="O14" s="6">
-        <v>100570.19662784383</v>
+        <v>77649.71602953106</v>
       </c>
       <c r="P14" s="6">
-        <v>101167.57567502964</v>
+        <v>76840.404873223495</v>
       </c>
       <c r="Q14" s="6">
-        <v>101768.50310670689</v>
+        <v>76039.528835306759</v>
       </c>
       <c r="R14" s="6">
-        <v>102373.00000000001</v>
+        <v>75247</v>
       </c>
       <c r="S14" s="7">
-        <v>102650.68942847707</v>
+        <v>74799.739597114487</v>
       </c>
       <c r="T14" s="7">
-        <v>102929.13209676041</v>
+        <v>74355.137663908696</v>
       </c>
       <c r="U14" s="7">
-        <v>103208.33004803263</v>
+        <v>73913.178398713178</v>
       </c>
       <c r="V14" s="7">
-        <v>103488.28533101849</v>
+        <v>73473.846093781991</v>
       </c>
       <c r="W14" s="7">
-        <v>103768.99999999999</v>
+        <v>73037.125134734422</v>
       </c>
       <c r="X14" s="10">
-        <v>104059.56817143403</v>
-      </c>
-      <c r="Y14" s="10">
-        <v>104350.94997567027</v>
-      </c>
-      <c r="Z14" s="10">
-        <v>104643.14769099794</v>
-      </c>
-      <c r="AA14" s="10">
-        <v>104936.1636020858</v>
-      </c>
-      <c r="AB14" s="10">
-        <v>105230.00000000003</v>
+        <v>72603.000000000015</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:24">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2140,85 +1972,73 @@
         <v>15</v>
       </c>
       <c r="C15" s="8">
-        <v>9667</v>
+        <v>26547</v>
       </c>
       <c r="D15" s="9">
-        <v>9232.9299695540485</v>
+        <v>27000.816641181293</v>
       </c>
       <c r="E15" s="9">
-        <v>8818.3506592209906</v>
+        <v>27462.391203928604</v>
       </c>
       <c r="F15" s="9">
-        <v>8422.3868918545759</v>
+        <v>27931.856308647541</v>
       </c>
       <c r="G15" s="9">
-        <v>8044.2027877297278</v>
+        <v>28409.346842867941</v>
       </c>
       <c r="H15" s="9">
-        <v>7683.0000000000018</v>
+        <v>28894.999999999996</v>
       </c>
       <c r="I15" s="5">
-        <v>7455.0715667731893</v>
+        <v>29503.79970341198</v>
       </c>
       <c r="J15" s="5">
-        <v>7233.9049935845442</v>
+        <v>30125.426438451384</v>
       </c>
       <c r="K15" s="5">
-        <v>7019.2996790850866</v>
+        <v>30760.150462707781</v>
       </c>
       <c r="L15" s="5">
-        <v>6811.0609730843944</v>
+        <v>31408.247727930288</v>
       </c>
       <c r="M15" s="5">
-        <v>6609</v>
+        <v>32069.999999999985</v>
       </c>
       <c r="N15" s="6">
-        <v>6466.5938805436381</v>
+        <v>32623.931001634515</v>
       </c>
       <c r="O15" s="6">
-        <v>6327.2562287614501</v>
+        <v>33187.429809772671</v>
       </c>
       <c r="P15" s="6">
-        <v>6190.9209274535342</v>
+        <v>33760.661684927101</v>
       </c>
       <c r="Q15" s="6">
-        <v>6057.523284067267</v>
+        <v>34343.794742082559</v>
       </c>
       <c r="R15" s="6">
-        <v>5926.9999999999982</v>
+        <v>34936.999999999985</v>
       </c>
       <c r="S15" s="7">
-        <v>5861.7803778496063</v>
+        <v>35184.73332015895</v>
       </c>
       <c r="T15" s="7">
-        <v>5797.278420472865</v>
+        <v>35434.223282213796</v>
       </c>
       <c r="U15" s="7">
-        <v>5733.4862308180864</v>
+        <v>35685.482342263495</v>
       </c>
       <c r="V15" s="7">
-        <v>5670.3959987312901</v>
+        <v>35938.523044731439</v>
       </c>
       <c r="W15" s="7">
-        <v>5608</v>
+        <v>36193.358022991742</v>
       </c>
       <c r="X15" s="10">
-        <v>5574.8094463976586</v>
-      </c>
-      <c r="Y15" s="10">
-        <v>5541.8153287525975</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>5509.0164844724186</v>
-      </c>
-      <c r="AA15" s="10">
-        <v>5476.4117578454452</v>
-      </c>
-      <c r="AB15" s="10">
-        <v>5443.9999999999991</v>
+        <v>36449.999999999993</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:24">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2226,85 +2046,73 @@
         <v>16</v>
       </c>
       <c r="C16" s="8">
-        <v>14158</v>
+        <v>7675</v>
       </c>
       <c r="D16" s="9">
-        <v>14090.764429340054</v>
+        <v>8081.7427795768544</v>
       </c>
       <c r="E16" s="9">
-        <v>14023.848156742119</v>
+        <v>8510.0412189241197</v>
       </c>
       <c r="F16" s="9">
-        <v>13957.249665877094</v>
+        <v>8961.037677516797</v>
       </c>
       <c r="G16" s="9">
-        <v>13890.967447616846</v>
+        <v>9435.9350550863219</v>
       </c>
       <c r="H16" s="9">
-        <v>13825.000000000002</v>
+        <v>9936.0000000000018</v>
       </c>
       <c r="I16" s="5">
-        <v>13922.028451806264</v>
+        <v>10364.594976779315</v>
       </c>
       <c r="J16" s="5">
-        <v>14019.737881584311</v>
+        <v>10811.677640164957</v>
       </c>
       <c r="K16" s="5">
-        <v>14118.133068664221</v>
+        <v>11278.045466969701</v>
       </c>
       <c r="L16" s="5">
-        <v>14217.218825918999</v>
+        <v>11764.530333619452</v>
       </c>
       <c r="M16" s="5">
-        <v>14316.999999999996</v>
+        <v>12272.000000000005</v>
       </c>
       <c r="N16" s="6">
-        <v>14464.528130497585</v>
+        <v>12476.097406424395</v>
       </c>
       <c r="O16" s="6">
-        <v>14613.576450230912</v>
+        <v>12683.589186325742</v>
       </c>
       <c r="P16" s="6">
-        <v>14764.160623841732</v>
+        <v>12894.531792020134</v>
       </c>
       <c r="Q16" s="6">
-        <v>14916.29647738657</v>
+        <v>13108.982614690294</v>
       </c>
       <c r="R16" s="6">
-        <v>15070.000000000005</v>
+        <v>13327.000000000004</v>
       </c>
       <c r="S16" s="7">
-        <v>15219.600199914556</v>
+        <v>13501.987668529397</v>
       </c>
       <c r="T16" s="7">
-        <v>15370.685484090191</v>
+        <v>13679.272979749372</v>
       </c>
       <c r="U16" s="7">
-        <v>15523.270594988908</v>
+        <v>13858.886102425406</v>
       </c>
       <c r="V16" s="7">
-        <v>15677.370421421429</v>
+        <v>14040.857601448282</v>
       </c>
       <c r="W16" s="7">
-        <v>15833.000000000007</v>
+        <v>14225.218443035337</v>
       </c>
       <c r="X16" s="10">
-        <v>15994.280634469729</v>
-      </c>
-      <c r="Y16" s="10">
-        <v>16157.20413150845</v>
-      </c>
-      <c r="Z16" s="10">
-        <v>16321.787225905373</v>
-      </c>
-      <c r="AA16" s="10">
-        <v>16488.046822916287</v>
-      </c>
-      <c r="AB16" s="10">
-        <v>16656</v>
+        <v>14412.000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2312,85 +2120,73 @@
         <v>17</v>
       </c>
       <c r="C17" s="8">
-        <v>33043</v>
+        <v>42274</v>
       </c>
       <c r="D17" s="9">
-        <v>32742.794419059766</v>
+        <v>43402.697689966357</v>
       </c>
       <c r="E17" s="9">
-        <v>32445.316296002522</v>
+        <v>44561.531124724672</v>
       </c>
       <c r="F17" s="9">
-        <v>32150.540851054087</v>
+        <v>45751.30491575085</v>
       </c>
       <c r="G17" s="9">
-        <v>31858.443529571974</v>
+        <v>46972.845157302494</v>
       </c>
       <c r="H17" s="9">
-        <v>31568.999999999996</v>
+        <v>48227.000000000007</v>
       </c>
       <c r="I17" s="5">
-        <v>31315.976442064704</v>
+        <v>48421.426019439699</v>
       </c>
       <c r="J17" s="5">
-        <v>31064.980852100212</v>
+        <v>48616.635862816926</v>
       </c>
       <c r="K17" s="5">
-        <v>30815.996976070241</v>
+        <v>48812.632690099497</v>
       </c>
       <c r="L17" s="5">
-        <v>30569.008690213592</v>
+        <v>49009.419673994576</v>
       </c>
       <c r="M17" s="5">
-        <v>30324.000000000004</v>
+        <v>49207.000000000015</v>
       </c>
       <c r="N17" s="6">
-        <v>30253.674567332269</v>
+        <v>49369.917626515409</v>
       </c>
       <c r="O17" s="6">
-        <v>30183.512228797237</v>
+        <v>49533.374650942278</v>
       </c>
       <c r="P17" s="6">
-        <v>30113.512606157681</v>
+        <v>49697.372859153103</v>
       </c>
       <c r="Q17" s="6">
-        <v>30043.675322053565</v>
+        <v>49861.914042933146</v>
       </c>
       <c r="R17" s="6">
-        <v>29974</v>
+        <v>50027.000000000022</v>
       </c>
       <c r="S17" s="7">
-        <v>30043.47716830319</v>
+        <v>50408.967654785447</v>
       </c>
       <c r="T17" s="7">
-        <v>30113.115378740076</v>
+        <v>50793.85172049504</v>
       </c>
       <c r="U17" s="7">
-        <v>30182.915004592553</v>
+        <v>51181.67446459717</v>
       </c>
       <c r="V17" s="7">
-        <v>30252.876420007746</v>
+        <v>51572.45832457747</v>
       </c>
       <c r="W17" s="7">
-        <v>30323.000000000022</v>
+        <v>51966.225909236935</v>
       </c>
       <c r="X17" s="10">
-        <v>30417.805323054472</v>
-      </c>
-      <c r="Y17" s="10">
-        <v>30512.907056400763</v>
-      </c>
-      <c r="Z17" s="10">
-        <v>30608.306126770203</v>
-      </c>
-      <c r="AA17" s="10">
-        <v>30704.003463791541</v>
-      </c>
-      <c r="AB17" s="10">
-        <v>30800.000000000022</v>
+        <v>52362.999999999964</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2398,85 +2194,73 @@
         <v>18</v>
       </c>
       <c r="C18" s="8">
-        <v>46515</v>
+        <v>25656</v>
       </c>
       <c r="D18" s="9">
-        <v>47239.854066393273</v>
+        <v>26795.065319598161</v>
       </c>
       <c r="E18" s="9">
-        <v>47976.003702335438</v>
+        <v>27984.702427562057</v>
       </c>
       <c r="F18" s="9">
-        <v>48723.624929314617</v>
+        <v>29227.156590896575</v>
       </c>
       <c r="G18" s="9">
-        <v>49482.896511802726</v>
+        <v>30524.772761116215</v>
       </c>
       <c r="H18" s="9">
-        <v>50254.000000000029</v>
+        <v>31879.999999999989</v>
       </c>
       <c r="I18" s="5">
-        <v>50883.43389028305</v>
+        <v>33011.916487321098</v>
       </c>
       <c r="J18" s="5">
-        <v>51520.751471859068</v>
+        <v>34184.022276219031</v>
       </c>
       <c r="K18" s="5">
-        <v>52166.051488360012</v>
+        <v>35397.744309387293</v>
       </c>
       <c r="L18" s="5">
-        <v>52819.433920186821</v>
+        <v>36654.560193884536</v>
       </c>
       <c r="M18" s="5">
-        <v>53481.000000000007</v>
+        <v>37956.000000000022</v>
       </c>
       <c r="N18" s="6">
-        <v>54097.998459473376</v>
+        <v>39162.959996244499</v>
       </c>
       <c r="O18" s="6">
-        <v>54722.115093606772</v>
+        <v>40408.300022854019</v>
       </c>
       <c r="P18" s="6">
-        <v>55353.4320232057</v>
+        <v>41693.240523534558</v>
       </c>
       <c r="Q18" s="6">
-        <v>55992.032316485223</v>
+        <v>43019.040750789965</v>
       </c>
       <c r="R18" s="6">
-        <v>56638.000000000022</v>
+        <v>44386.999999999985</v>
       </c>
       <c r="S18" s="7">
-        <v>57157.000741939402</v>
+        <v>45485.279145486566</v>
       </c>
       <c r="T18" s="7">
-        <v>57680.757332781192</v>
+        <v>46610.73329900275</v>
       </c>
       <c r="U18" s="7">
-        <v>58209.313352614874</v>
+        <v>47764.034858876832</v>
       </c>
       <c r="V18" s="7">
-        <v>58742.712780874877</v>
+        <v>48945.872860764721</v>
       </c>
       <c r="W18" s="7">
-        <v>59280.999999999971</v>
+        <v>50156.953389311697</v>
       </c>
       <c r="X18" s="10">
-        <v>59953.373702520039</v>
-      </c>
-      <c r="Y18" s="10">
-        <v>60633.373565122442</v>
-      </c>
-      <c r="Z18" s="10">
-        <v>61321.086084821232</v>
-      </c>
-      <c r="AA18" s="10">
-        <v>62016.598739692156</v>
-      </c>
-      <c r="AB18" s="10">
-        <v>62719.999999999985</v>
+        <v>51398.000000000022</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2484,85 +2268,73 @@
         <v>19</v>
       </c>
       <c r="C19" s="8">
-        <v>17568</v>
+        <v>25109</v>
       </c>
       <c r="D19" s="9">
-        <v>17013.254479956282</v>
+        <v>25915.852027895555</v>
       </c>
       <c r="E19" s="9">
-        <v>16476.026183956765</v>
+        <v>26748.631420278711</v>
       </c>
       <c r="F19" s="9">
-        <v>15955.761969836032</v>
+        <v>27608.171326482963</v>
       </c>
       <c r="G19" s="9">
-        <v>15451.926162023505</v>
+        <v>28495.331668243314</v>
       </c>
       <c r="H19" s="9">
-        <v>14964.000000000002</v>
+        <v>29410.999999999996</v>
       </c>
       <c r="I19" s="5">
-        <v>14911.83760393551</v>
+        <v>30206.218989812525</v>
       </c>
       <c r="J19" s="5">
-        <v>14859.857038635735</v>
+        <v>31022.93922887732</v>
       </c>
       <c r="K19" s="5">
-        <v>14808.057670264243</v>
+        <v>31861.74207116773</v>
       </c>
       <c r="L19" s="5">
-        <v>14756.438867194065</v>
+        <v>32723.224589392248</v>
       </c>
       <c r="M19" s="5">
-        <v>14704.999999999998</v>
+        <v>33608.000000000015</v>
       </c>
       <c r="N19" s="6">
-        <v>14713.390419677338</v>
+        <v>34075.037855755814</v>
       </c>
       <c r="O19" s="6">
-        <v>14721.785626783603</v>
+        <v>34548.565962603898</v>
       </c>
       <c r="P19" s="6">
-        <v>14730.185624050418</v>
+        <v>35028.674513145816</v>
       </c>
       <c r="Q19" s="6">
-        <v>14738.590414210967</v>
+        <v>35515.454953356122</v>
       </c>
       <c r="R19" s="6">
-        <v>14746.999999999993</v>
+        <v>36009.000000000007</v>
       </c>
       <c r="S19" s="7">
-        <v>14759.977140511834</v>
+        <v>36279.694739265069</v>
       </c>
       <c r="T19" s="7">
-        <v>14772.96570071417</v>
+        <v>36552.424404294965</v>
       </c>
       <c r="U19" s="7">
-        <v>14785.96569065617</v>
+        <v>36827.204292479219</v>
       </c>
       <c r="V19" s="7">
-        <v>14798.977120395832</v>
+        <v>37104.049816204235</v>
       </c>
       <c r="W19" s="7">
-        <v>14812.000000000007</v>
+        <v>37382.976503717786</v>
       </c>
       <c r="X19" s="10">
-        <v>14820.989082816275</v>
-      </c>
-      <c r="Y19" s="10">
-        <v>14829.983620912712</v>
-      </c>
-      <c r="Z19" s="10">
-        <v>14838.98361760001</v>
-      </c>
-      <c r="AA19" s="10">
-        <v>14847.989076190872</v>
-      </c>
-      <c r="AB19" s="10">
-        <v>14857.000000000007</v>
+        <v>37663.999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2570,85 +2342,73 @@
         <v>20</v>
       </c>
       <c r="C20" s="8">
-        <v>15353</v>
+        <v>14833</v>
       </c>
       <c r="D20" s="9">
-        <v>15954.23064106446</v>
+        <v>15912.286605658135</v>
       </c>
       <c r="E20" s="9">
-        <v>16579.005754463626</v>
+        <v>17070.104835205777</v>
       </c>
       <c r="F20" s="9">
-        <v>17228.247352715924</v>
+        <v>18312.168848272435</v>
       </c>
       <c r="G20" s="9">
-        <v>17902.913554780047</v>
+        <v>19644.608581198383</v>
       </c>
       <c r="H20" s="9">
-        <v>18604.000000000004</v>
+        <v>21073.999999999993</v>
       </c>
       <c r="I20" s="5">
-        <v>19208.780355778479</v>
+        <v>22218.703138578177</v>
       </c>
       <c r="J20" s="5">
-        <v>19833.220960897721</v>
+        <v>23425.584566777252</v>
       </c>
       <c r="K20" s="5">
-        <v>20477.960932353588</v>
+        <v>24698.021701474911</v>
       </c>
       <c r="L20" s="5">
-        <v>21143.660163609587</v>
+        <v>26039.575414977346</v>
       </c>
       <c r="M20" s="5">
-        <v>21830.999999999993</v>
+        <v>27454.000000000015</v>
       </c>
       <c r="N20" s="6">
-        <v>22383.516157218663</v>
+        <v>28560.534085302159</v>
       </c>
       <c r="O20" s="6">
-        <v>22950.015828888689</v>
+        <v>29711.667051712189</v>
       </c>
       <c r="P20" s="6">
-        <v>23530.852920816913</v>
+        <v>30909.196458132697</v>
       </c>
       <c r="Q20" s="6">
-        <v>24126.390295737318</v>
+        <v>32154.99231411815</v>
       </c>
       <c r="R20" s="6">
-        <v>24736.999999999993</v>
+        <v>33451.000000000015</v>
       </c>
       <c r="S20" s="7">
-        <v>25238.084212872243</v>
+        <v>34401.094044339923</v>
       </c>
       <c r="T20" s="7">
-        <v>25749.318621337719</v>
+        <v>35378.173192057628</v>
       </c>
       <c r="U20" s="7">
-        <v>26270.908832493864</v>
+        <v>36383.003889178799</v>
       </c>
       <c r="V20" s="7">
-        <v>26803.064618311411</v>
+        <v>37416.374350758575</v>
       </c>
       <c r="W20" s="7">
-        <v>27345.999999999993</v>
+        <v>38479.095179177719</v>
       </c>
       <c r="X20" s="10">
-        <v>27798.944729873965</v>
-      </c>
-      <c r="Y20" s="10">
-        <v>28259.391797505585</v>
-      </c>
-      <c r="Z20" s="10">
-        <v>28727.465467662973</v>
-      </c>
-      <c r="AA20" s="10">
-        <v>29203.292063370369</v>
-      </c>
-      <c r="AB20" s="10">
-        <v>29687.000000000004</v>
+        <v>39571.999999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2656,85 +2416,73 @@
         <v>21</v>
       </c>
       <c r="C21" s="8">
-        <v>40045</v>
+        <v>39002</v>
       </c>
       <c r="D21" s="9">
-        <v>41478.959761209633</v>
+        <v>40793.821827735133</v>
       </c>
       <c r="E21" s="9">
-        <v>42964.267770559323</v>
+        <v>42667.963163760818</v>
       </c>
       <c r="F21" s="9">
-        <v>44502.762742536303</v>
+        <v>44628.205913922997</v>
       </c>
       <c r="G21" s="9">
-        <v>46096.34923362024</v>
+        <v>46678.505731604797</v>
       </c>
       <c r="H21" s="9">
-        <v>47747.000000000015</v>
+        <v>48822.999999999985</v>
       </c>
       <c r="I21" s="5">
-        <v>48870.471446772128</v>
+        <v>50187.919731285285</v>
       </c>
       <c r="J21" s="5">
-        <v>50020.37781284206</v>
+        <v>51590.997827948609</v>
       </c>
       <c r="K21" s="5">
-        <v>51197.341103299725</v>
+        <v>53033.301063965722</v>
       </c>
       <c r="L21" s="5">
-        <v>52401.997958813372</v>
+        <v>54515.926036568795</v>
       </c>
       <c r="M21" s="5">
-        <v>53635</v>
+        <v>56040.000000000007</v>
       </c>
       <c r="N21" s="6">
-        <v>54766.813906852585</v>
+        <v>57181.352192949118</v>
       </c>
       <c r="O21" s="6">
-        <v>55922.511522472669</v>
+        <v>58345.950010958011</v>
       </c>
       <c r="P21" s="6">
-        <v>57102.596844506013</v>
+        <v>59534.266891662985</v>
       </c>
       <c r="Q21" s="6">
-        <v>58307.584506033156</v>
+        <v>60746.785915082284</v>
       </c>
       <c r="R21" s="6">
-        <v>59537.999999999978</v>
+        <v>61984.000000000022</v>
       </c>
       <c r="S21" s="7">
-        <v>60586.233727839055</v>
+        <v>62851.725228157222</v>
       </c>
       <c r="T21" s="7">
-        <v>61652.922794254802</v>
+        <v>63731.597898744432</v>
       </c>
       <c r="U21" s="7">
-        <v>62738.392126324994</v>
+        <v>64623.788066005538</v>
       </c>
       <c r="V21" s="7">
-        <v>63842.972371835524</v>
+        <v>65528.468164804559</v>
       </c>
       <c r="W21" s="7">
-        <v>64966.999999999971</v>
+        <v>66445.813043952381</v>
       </c>
       <c r="X21" s="10">
-        <v>65811.744621774938</v>
-      </c>
-      <c r="Y21" s="10">
-        <v>66667.473181180045</v>
-      </c>
-      <c r="Z21" s="10">
-        <v>67534.328498758638</v>
-      </c>
-      <c r="AA21" s="10">
-        <v>68412.455252102794</v>
-      </c>
-      <c r="AB21" s="10">
-        <v>69301.999999999942</v>
+        <v>67376</v>
       </c>
     </row>
-    <row r="22" spans="1:28">
+    <row r="22" spans="1:24">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2742,85 +2490,73 @@
         <v>22</v>
       </c>
       <c r="C22" s="8">
-        <v>3918</v>
+        <v>3898</v>
       </c>
       <c r="D22" s="9">
-        <v>3970.3805757953282</v>
+        <v>4156.8592515256441</v>
       </c>
       <c r="E22" s="9">
-        <v>4023.4614386556514</v>
+        <v>4432.9088858374398</v>
       </c>
       <c r="F22" s="9">
-        <v>4077.2519508677701</v>
+        <v>4727.2904857012818</v>
       </c>
       <c r="G22" s="9">
-        <v>4131.7615998848905</v>
+        <v>5041.2214443654511</v>
       </c>
       <c r="H22" s="9">
-        <v>4186.9999999999991</v>
+        <v>5375.9999999999991</v>
       </c>
       <c r="I22" s="5">
-        <v>4231.2545613265129</v>
+        <v>5612.4631048679612</v>
       </c>
       <c r="J22" s="5">
-        <v>4275.9768719241511</v>
+        <v>5859.3270281815685</v>
       </c>
       <c r="K22" s="5">
-        <v>4321.1718756760774</v>
+        <v>6117.0492494465561</v>
       </c>
       <c r="L22" s="5">
-        <v>4366.8445687199055</v>
+        <v>6386.107370383007</v>
       </c>
       <c r="M22" s="5">
-        <v>4413.0000000000018</v>
+        <v>6666.9999999999964</v>
       </c>
       <c r="N22" s="6">
-        <v>4449.3947224417807</v>
+        <v>6766.957427714985</v>
       </c>
       <c r="O22" s="6">
-        <v>4486.0895980269142</v>
+        <v>6868.4135036008711</v>
       </c>
       <c r="P22" s="6">
-        <v>4523.0871021667626</v>
+        <v>6971.390696686638</v>
       </c>
       <c r="Q22" s="6">
-        <v>4560.3897306878043</v>
+        <v>7075.9118128763748</v>
       </c>
       <c r="R22" s="6">
-        <v>4598.0000000000027</v>
+        <v>7181.9999999999982</v>
       </c>
       <c r="S22" s="7">
-        <v>4629.1743998851907</v>
+        <v>7214.1383129835658</v>
       </c>
       <c r="T22" s="7">
-        <v>4660.5601619296249</v>
+        <v>7246.4204398297652</v>
       </c>
       <c r="U22" s="7">
-        <v>4692.1587191668987</v>
+        <v>7278.8470240828647</v>
       </c>
       <c r="V22" s="7">
-        <v>4723.9715143465628</v>
+        <v>7311.4187121668911</v>
       </c>
       <c r="W22" s="7">
-        <v>4755.9999999999973</v>
+        <v>7344.1361533985146</v>
       </c>
       <c r="X22" s="10">
-        <v>4772.4853198474093</v>
-      </c>
-      <c r="Y22" s="10">
-        <v>4789.0277813622879</v>
-      </c>
-      <c r="Z22" s="10">
-        <v>4805.6275826099536</v>
-      </c>
-      <c r="AA22" s="10">
-        <v>4822.2849223422645</v>
-      </c>
-      <c r="AB22" s="10">
-        <v>4838.9999999999945</v>
+        <v>7376.9999999999964</v>
       </c>
     </row>
-    <row r="23" spans="1:28">
+    <row r="23" spans="1:24">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2831,82 +2567,70 @@
         <v>25332</v>
       </c>
       <c r="D23" s="9">
-        <v>25313.573211777675</v>
+        <v>25291.269230199789</v>
       </c>
       <c r="E23" s="9">
-        <v>25295.159827413088</v>
+        <v>25250.603950515182</v>
       </c>
       <c r="F23" s="9">
-        <v>25276.759837156118</v>
+        <v>25210.004055646055</v>
       </c>
       <c r="G23" s="9">
-        <v>25258.373231263737</v>
+        <v>25169.469440461588</v>
       </c>
       <c r="H23" s="9">
-        <v>25240.000000000004</v>
+        <v>25129</v>
       </c>
       <c r="I23" s="5">
-        <v>25221.773695850821</v>
+        <v>25088.670759723966</v>
       </c>
       <c r="J23" s="5">
-        <v>25203.560553277035</v>
+        <v>25048.406243377303</v>
       </c>
       <c r="K23" s="5">
-        <v>25185.360562774407</v>
+        <v>25008.206347085332</v>
       </c>
       <c r="L23" s="5">
-        <v>25167.173714845569</v>
+        <v>24968.070967140076</v>
       </c>
       <c r="M23" s="5">
-        <v>25149.000000000007</v>
+        <v>24928.000000000004</v>
       </c>
       <c r="N23" s="6">
-        <v>25130.97417810321</v>
+        <v>24895.71648939537</v>
       </c>
       <c r="O23" s="6">
-        <v>25112.961276412196</v>
+        <v>24863.47478820413</v>
       </c>
       <c r="P23" s="6">
-        <v>25094.961285666257</v>
+        <v>24831.274842280152</v>
       </c>
       <c r="Q23" s="6">
-        <v>25076.974196611332</v>
+        <v>24799.116597547432</v>
       </c>
       <c r="R23" s="6">
-        <v>25058.999999999996</v>
+        <v>24767</v>
       </c>
       <c r="S23" s="7">
-        <v>25043.180038050396</v>
+        <v>24760.662614019868</v>
       </c>
       <c r="T23" s="7">
-        <v>25027.370063378658</v>
+        <v>24754.326849651599</v>
       </c>
       <c r="U23" s="7">
-        <v>25011.570069679732</v>
+        <v>24747.992706480258</v>
       </c>
       <c r="V23" s="7">
-        <v>24995.780050652545</v>
+        <v>24741.660184091012</v>
       </c>
       <c r="W23" s="7">
-        <v>24980.000000000004</v>
+        <v>24735.329282069131</v>
       </c>
       <c r="X23" s="10">
-        <v>24977.799612387578</v>
-      </c>
-      <c r="Y23" s="10">
-        <v>24975.599418598438</v>
-      </c>
-      <c r="Z23" s="10">
-        <v>24973.399418615511</v>
-      </c>
-      <c r="AA23" s="10">
-        <v>24971.199612421722</v>
-      </c>
-      <c r="AB23" s="10">
-        <v>24969.000000000004</v>
+        <v>24729</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:24">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2917,82 +2641,70 @@
         <v>2737</v>
       </c>
       <c r="D24" s="9">
-        <v>2717.318986465772</v>
+        <v>2710.6993731220946</v>
       </c>
       <c r="E24" s="9">
-        <v>2697.7794936819037</v>
+        <v>2684.6514765964621</v>
       </c>
       <c r="F24" s="9">
-        <v>2678.3805040116385</v>
+        <v>2658.8538818638422</v>
       </c>
       <c r="G24" s="9">
-        <v>2659.121007135765</v>
+        <v>2633.3041837017045</v>
       </c>
       <c r="H24" s="9">
-        <v>2640</v>
+        <v>2608</v>
       </c>
       <c r="I24" s="5">
-        <v>2625.2357829982102</v>
+        <v>2615.1605715062242</v>
       </c>
       <c r="J24" s="5">
-        <v>2610.5541349750856</v>
+        <v>2622.3408032058132</v>
       </c>
       <c r="K24" s="5">
-        <v>2595.9545941630809</v>
+        <v>2629.5407490781463</v>
       </c>
       <c r="L24" s="5">
-        <v>2581.4367013770893</v>
+        <v>2636.7604632508092</v>
       </c>
       <c r="M24" s="5">
-        <v>2567</v>
+        <v>2644.0000000000009</v>
       </c>
       <c r="N24" s="6">
-        <v>2558.74710427322</v>
+        <v>2664.6741485472935</v>
       </c>
       <c r="O24" s="6">
-        <v>2550.520741576388</v>
+        <v>2685.5099538336776</v>
       </c>
       <c r="P24" s="6">
-        <v>2542.3208266059091</v>
+        <v>2706.5086798967614</v>
       </c>
       <c r="Q24" s="6">
-        <v>2534.1472743324384</v>
+        <v>2727.6716006580041</v>
       </c>
       <c r="R24" s="6">
-        <v>2526</v>
+        <v>2749</v>
       </c>
       <c r="S24" s="7">
-        <v>2527.1988614796915</v>
+        <v>2775.3599535568051</v>
       </c>
       <c r="T24" s="7">
-        <v>2528.3982919494256</v>
+        <v>2801.9726707191094</v>
       </c>
       <c r="U24" s="7">
-        <v>2529.59829167925</v>
+        <v>2828.840575218052</v>
       </c>
       <c r="V24" s="7">
-        <v>2530.7988609393401</v>
+        <v>2855.9661140257472</v>
       </c>
       <c r="W24" s="7">
-        <v>2532</v>
+        <v>2883.3517575781398</v>
       </c>
       <c r="X24" s="10">
-        <v>2533.3984543798629</v>
-      </c>
-      <c r="Y24" s="10">
-        <v>2534.7976811430799</v>
-      </c>
-      <c r="Z24" s="10">
-        <v>2536.1976807162478</v>
-      </c>
-      <c r="AA24" s="10">
-        <v>2537.5984535261987</v>
-      </c>
-      <c r="AB24" s="10">
-        <v>2539.0000000000009</v>
+        <v>2910.9999999999995</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:24">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3000,85 +2712,73 @@
         <v>25</v>
       </c>
       <c r="C25" s="8">
-        <v>3743</v>
+        <v>3747</v>
       </c>
       <c r="D25" s="9">
-        <v>3785.2360016273974</v>
+        <v>3954.5080436160583</v>
       </c>
       <c r="E25" s="9">
-        <v>3827.9485941801136</v>
+        <v>4173.5078374764089</v>
       </c>
       <c r="F25" s="9">
-        <v>3871.1431555088298</v>
+        <v>4404.6357922057969</v>
       </c>
       <c r="G25" s="9">
-        <v>3914.8251241478783</v>
+        <v>4648.5635627107049</v>
       </c>
       <c r="H25" s="9">
-        <v>3958.9999999999986</v>
+        <v>4906.0000000000009</v>
       </c>
       <c r="I25" s="5">
-        <v>3995.1343457194093</v>
+        <v>5032.1441590964951</v>
       </c>
       <c r="J25" s="5">
-        <v>4031.598494656947</v>
+        <v>5161.5317647633456</v>
       </c>
       <c r="K25" s="5">
-        <v>4068.3954569726288</v>
+        <v>5294.2462132174669</v>
       </c>
       <c r="L25" s="5">
-        <v>4105.5282703006214</v>
+        <v>5430.373044977785</v>
       </c>
       <c r="M25" s="5">
-        <v>4143.0000000000027</v>
+        <v>5570.0000000000018</v>
       </c>
       <c r="N25" s="6">
-        <v>4171.2131213202165</v>
+        <v>5675.7106491504564</v>
       </c>
       <c r="O25" s="6">
-        <v>4199.6183691706356</v>
+        <v>5783.4275355260133</v>
       </c>
       <c r="P25" s="6">
-        <v>4228.2170519000629</v>
+        <v>5893.1887346454168</v>
       </c>
       <c r="Q25" s="6">
-        <v>4257.0104867669379</v>
+        <v>6005.0330446464077</v>
       </c>
       <c r="R25" s="6">
-        <v>4286.0000000000027</v>
+        <v>6119</v>
       </c>
       <c r="S25" s="7">
-        <v>4311.6901759474558</v>
+        <v>6199.4739312346783</v>
       </c>
       <c r="T25" s="7">
-        <v>4337.5343381618768</v>
+        <v>6281.0062140968066</v>
       </c>
       <c r="U25" s="7">
-        <v>4363.5334096330644</v>
+        <v>6363.6107674809891</v>
       </c>
       <c r="V25" s="7">
-        <v>4389.6883188831989</v>
+        <v>6447.3016933359531</v>
       </c>
       <c r="W25" s="7">
-        <v>4415.9999999999982</v>
+        <v>6532.0932790719789</v>
       </c>
       <c r="X25" s="10">
-        <v>4434.4452663386492</v>
-      </c>
-      <c r="Y25" s="10">
-        <v>4452.9675770274598</v>
-      </c>
-      <c r="Z25" s="10">
-        <v>4471.5672538743001</v>
-      </c>
-      <c r="AA25" s="10">
-        <v>4490.244620031207</v>
-      </c>
-      <c r="AB25" s="10">
-        <v>4508.9999999999955</v>
+        <v>6617.9999999999973</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:24">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3089,82 +2789,70 @@
         <v>11723</v>
       </c>
       <c r="D26" s="9">
-        <v>11772.382206535018</v>
+        <v>11640.445444042622</v>
       </c>
       <c r="E26" s="9">
-        <v>11821.972431693448</v>
+        <v>11558.472245648096</v>
       </c>
       <c r="F26" s="9">
-        <v>11871.771551737223</v>
+        <v>11477.076310837454</v>
       </c>
       <c r="G26" s="9">
-        <v>11921.780446619459</v>
+        <v>11396.253574461942</v>
       </c>
       <c r="H26" s="9">
-        <v>11972.000000000002</v>
+        <v>11315.999999999996</v>
       </c>
       <c r="I26" s="5">
-        <v>11989.946116565867</v>
+        <v>11206.50128885433</v>
       </c>
       <c r="J26" s="5">
-        <v>12007.919134493226</v>
+        <v>11098.06213654063</v>
       </c>
       <c r="K26" s="5">
-        <v>12025.919094107419</v>
+        <v>10990.672290290562</v>
       </c>
       <c r="L26" s="5">
-        <v>12043.946035794233</v>
+        <v>10884.321596546197</v>
       </c>
       <c r="M26" s="5">
-        <v>12061.999999999995</v>
+        <v>10778.999999999998</v>
       </c>
       <c r="N26" s="6">
-        <v>12076.76381409977</v>
+        <v>10750.651277624618</v>
       </c>
       <c r="O26" s="6">
-        <v>12091.545699017544</v>
+        <v>10722.37711226383</v>
       </c>
       <c r="P26" s="6">
-        <v>12106.345676871893</v>
+        <v>10694.177307833019</v>
       </c>
       <c r="Q26" s="6">
-        <v>12121.163769808461</v>
+        <v>10666.051668763266</v>
       </c>
       <c r="R26" s="6">
-        <v>12135.999999999998</v>
+        <v>10638</v>
       </c>
       <c r="S26" s="7">
-        <v>12146.980113378526</v>
+        <v>10669.105070108708</v>
       </c>
       <c r="T26" s="7">
-        <v>12157.970161075593</v>
+        <v>10700.301090150342</v>
       </c>
       <c r="U26" s="7">
-        <v>12168.97015207933</v>
+        <v>10731.588326058727</v>
       </c>
       <c r="V26" s="7">
-        <v>12179.980095385998</v>
+        <v>10762.96704454527</v>
       </c>
       <c r="W26" s="7">
-        <v>12191</v>
+        <v>10794.437513101229</v>
       </c>
       <c r="X26" s="10">
-        <v>12219.070434634399</v>
-      </c>
-      <c r="Y26" s="10">
-        <v>12247.205502957631</v>
-      </c>
-      <c r="Z26" s="10">
-        <v>12275.405353792248</v>
-      </c>
-      <c r="AA26" s="10">
-        <v>12303.670136303475</v>
-      </c>
-      <c r="AB26" s="10">
-        <v>12331.999999999998</v>
+        <v>10825.999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:24">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3175,82 +2863,70 @@
         <v>2985</v>
       </c>
       <c r="D27" s="9">
-        <v>2951.454453337707</v>
+        <v>3010.5585547979663</v>
       </c>
       <c r="E27" s="9">
-        <v>2918.28589283986</v>
+        <v>3036.3359503742777</v>
       </c>
       <c r="F27" s="9">
-        <v>2885.4900819212098</v>
+        <v>3062.3340605158778</v>
       </c>
       <c r="G27" s="9">
-        <v>2853.0628316074167</v>
+        <v>3088.5547750536916</v>
       </c>
       <c r="H27" s="9">
-        <v>2820.9999999999995</v>
+        <v>3115</v>
       </c>
       <c r="I27" s="5">
-        <v>2854.3996981037726</v>
+        <v>3205.0418624029762</v>
       </c>
       <c r="J27" s="5">
-        <v>2888.1948374813574</v>
+        <v>3297.6864654110877</v>
       </c>
       <c r="K27" s="5">
-        <v>2922.3901000254027</v>
+        <v>3393.0090435705429</v>
       </c>
       <c r="L27" s="5">
-        <v>2956.990223060604</v>
+        <v>3491.0870061494297</v>
       </c>
       <c r="M27" s="5">
-        <v>2991.9999999999986</v>
+        <v>3591.9999999999995</v>
       </c>
       <c r="N27" s="6">
-        <v>3028.308042412028</v>
+        <v>3669.9432044678788</v>
       </c>
       <c r="O27" s="6">
-        <v>3065.056684404201</v>
+        <v>3749.5777071325065</v>
       </c>
       <c r="P27" s="6">
-        <v>3102.2512726704499</v>
+        <v>3830.9402076601314</v>
       </c>
       <c r="Q27" s="6">
-        <v>3139.8972187870563</v>
+        <v>3914.0682020671111</v>
       </c>
       <c r="R27" s="6">
-        <v>3178.0000000000005</v>
+        <v>3999.0000000000005</v>
       </c>
       <c r="S27" s="7">
-        <v>3214.9316010812063</v>
+        <v>4051.5747455944156</v>
       </c>
       <c r="T27" s="7">
-        <v>3252.2923850316452</v>
+        <v>4104.8406899571028</v>
       </c>
       <c r="U27" s="7">
-        <v>3290.0873393939592</v>
+        <v>4158.8069202597035</v>
       </c>
       <c r="V27" s="7">
-        <v>3328.3215096711224</v>
+        <v>4213.4826431426618</v>
       </c>
       <c r="W27" s="7">
-        <v>3366.9999999999995</v>
+        <v>4268.8771862858757</v>
       </c>
       <c r="X27" s="10">
-        <v>3398.0230254229891</v>
-      </c>
-      <c r="Y27" s="10">
-        <v>3429.3318922794197</v>
-      </c>
-      <c r="Z27" s="10">
-        <v>3460.9292342687436</v>
-      </c>
-      <c r="AA27" s="10">
-        <v>3492.8177093569188</v>
-      </c>
-      <c r="AB27" s="10">
-        <v>3524.9999999999982</v>
+        <v>4325.0000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:28">
+    <row r="28" spans="1:24">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3261,79 +2937,67 @@
         <v>247</v>
       </c>
       <c r="D28" s="9">
-        <v>248.38439417569799</v>
+        <v>256.27654031821203</v>
       </c>
       <c r="E28" s="9">
-        <v>249.77654765193731</v>
+        <v>265.90147820838928</v>
       </c>
       <c r="F28" s="9">
-        <v>251.17650391831501</v>
+        <v>275.88789838358076</v>
       </c>
       <c r="G28" s="9">
-        <v>252.58430670818018</v>
+        <v>286.2493769773543</v>
       </c>
       <c r="H28" s="9">
-        <v>254.00000000000011</v>
+        <v>297.00000000000006</v>
       </c>
       <c r="I28" s="5">
-        <v>255.77501746569328</v>
+        <v>307.43980821045039</v>
       </c>
       <c r="J28" s="5">
-        <v>257.56243921092795</v>
+        <v>318.24658475581992</v>
       </c>
       <c r="K28" s="5">
-        <v>259.36235192000652</v>
+        <v>329.43322889212163</v>
       </c>
       <c r="L28" s="5">
-        <v>261.17484288300375</v>
+        <v>341.01309329543193</v>
       </c>
       <c r="M28" s="5">
-        <v>262.99999999999994</v>
+        <v>353.00000000000006</v>
       </c>
       <c r="N28" s="6">
-        <v>265.55006692318477</v>
+        <v>358.80585322322975</v>
       </c>
       <c r="O28" s="6">
-        <v>268.12485947873728</v>
+        <v>364.7071963378184</v>
       </c>
       <c r="P28" s="6">
-        <v>270.72461740816806</v>
+        <v>370.70559988284111</v>
       </c>
       <c r="Q28" s="6">
-        <v>273.3495827775385</v>
+        <v>376.80266022830602</v>
       </c>
       <c r="R28" s="6">
-        <v>275.99999999999994</v>
+        <v>383.00000000000023</v>
       </c>
       <c r="S28" s="7">
-        <v>279.31920014019738</v>
+        <v>381.82434826054072</v>
       </c>
       <c r="T28" s="7">
-        <v>282.6783172715929</v>
+        <v>380.6523052861271</v>
       </c>
       <c r="U28" s="7">
-        <v>286.07783143941401</v>
+        <v>379.48385999934169</v>
       </c>
       <c r="V28" s="7">
-        <v>289.5182284619541</v>
+        <v>378.31900135677006</v>
       </c>
       <c r="W28" s="7">
-        <v>292.99999999999983</v>
+        <v>377.15771834889648</v>
       </c>
       <c r="X28" s="10">
-        <v>296.32373224848124</v>
-      </c>
-      <c r="Y28" s="10">
-        <v>299.68516823778032</v>
-      </c>
-      <c r="Z28" s="10">
-        <v>303.08473567144409</v>
-      </c>
-      <c r="AA28" s="10">
-        <v>306.52286710480121</v>
-      </c>
-      <c r="AB28" s="10">
-        <v>309.99999999999983</v>
+        <v>375.99999999999994</v>
       </c>
     </row>
   </sheetData>
